--- a/URLCanonique/ig/StructureDefinition-FRLMPatientEducation.xlsx
+++ b/URLCanonique/ig/StructureDefinition-FRLMPatientEducation.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-30T08:39:54+00:00</t>
+    <t>2026-09-30T08:56:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -385,7 +385,7 @@
 </t>
   </si>
   <si>
-    <t>Simple observation</t>
+    <t>Observation</t>
   </si>
   <si>
     <t>FRLMPatientEducation.entry.reference</t>
@@ -395,7 +395,7 @@
 </t>
   </si>
   <si>
-    <t>Références externes</t>
+    <t>Référence externe</t>
   </si>
 </sst>
 </file>
